--- a/Base_Datos_Agroecologica_Uruguay.xlsx
+++ b/Base_Datos_Agroecologica_Uruguay.xlsx
@@ -40,7 +40,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -78,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -86,45 +91,37 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -492,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -503,18 +500,18 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="36" customWidth="1" min="17" max="17"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -557,1599 +554,2444 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Temp_min_C</t>
+          <t>Temp_optima_C</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Temp_optima_C</t>
+          <t>Funcion_ecologica</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Temp_max_C</t>
+          <t>Compatible</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Funcion_ecologica</t>
+          <t>Incompatible</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Compatible</t>
+          <t>Region_Uruguay</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Incompatible</t>
+          <t>Tipo_sistema</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Region_Uruguay</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo_sistema</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Tomate</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Solanum lycopersicum</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Solanaceae</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Verano</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>26-29</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Produccion</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Albahaca;Caléndula;Zanahoria</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Papa;Hinojo</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Hortícola intensivo</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Referencia: INIA Las Brujas, Serie Actividades de Difusión No.537 (2008). Cosecha 85-120 días post-trasplante</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Cosecha 85-120 días post-trasplante. Temp óptima 20-24°C; detiene crecimiento &lt;13°C o &gt;30°C. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.108</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Morrón</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Capsicum annuum</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Solanaceae</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verano</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>20-25</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Produccion</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Albahaca;Zanahoria</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Papa</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Hortícola intensivo</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>Misma familia que tomate; almácigo 45 días antes del trasplante</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Misma familia que tomate; almácigo 45 días antes del trasplante. Sensible a heladas. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Berenjena</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Solanum melongena</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Solanaceae</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Verano</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>18-26</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Produccion</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Poroto;Albahaca</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Papa</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Hortícola intensivo</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Solanácea; no rotar con tomate ni papa</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="n">
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Solanácea; no rotar con tomate ni papa. Muy sensible a heladas y exigente en calor. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Maíz</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Zea mays</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Poaceae</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verano</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>25-35</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Soporte</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Poroto;Zapallo;Calabaza</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Hortícola;Policultivo</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>Base del sistema 3 Hermanas (maíz+poroto+zapallo). Ref: conocimiento indígena mesoamericano</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Base del sistema 3 Hermanas (maíz+poroto+zapallo). Sensible a heladas. Ref: conocimiento indígena mesoamericano; Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Poroto</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Phaseolus vulgaris</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Verano</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>19-26</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Fijacion_N</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>Maíz;Zanahoria;Pepino</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>Cebolla;Ajo</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Hortícola;Policultivo</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Fija nitrógeno atmosférico. Sistema 3 Hermanas</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="n">
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>Fija nitrógeno atmosférico. Sistema 3 Hermanas. Ref: conocimiento indígena mesoamericano; Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Zapallo</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Cucurbita maxima</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Cucurbitaceae</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verano</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>18-24</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Cobertura</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Maíz;Poroto</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Hortícola;Policultivo</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>Cobertura de suelo. Sistema 3 Hermanas</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>Cobertura de suelo. Sistema 3 Hermanas. Sensible a heladas. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Lechuga</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Lactuca sativa</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>15-24</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Produccion</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Zanahoria;Rábano;Cebolla</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Hortícola intensivo</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>Múltiples siembras escalonadas. Semillas no germinan &lt;5°C ni &gt;27°C. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.81; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Espinaca</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Spinacia oleracea</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Amaranthaceae</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Invierno</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Produccion</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Zanahoria;Rábano;Cebolla</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Ajo;Frutilla;Arveja</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Hortícola intensivo</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>Cultivo de estación fría; múltiples siembras escalonadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Espinaca</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Spinacia oleracea</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Amaranthaceae</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Invierno</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Medio</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Medio</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Produccion</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>Ajo;Frutilla;Arveja</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>Sur;Litoral</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Hortícola</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>Tolera heladas; buena bajo sombra de árboles agroforestales</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>Tolera heladas. Germina desde 4-5°C; óptimo 10-15°C. Produce principalmente otoño-invierno. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.77; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Acelga</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Beta vulgaris var. cicla</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Amaranthaceae</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>15-25</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>Produccion</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>Cebolla;Poroto</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>Hortícola</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Muy resistente; cosecha continua por hojas; tolera heladas moderadas</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="3" t="n">
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Muy resistente; cosecha continua por hojas; tolera heladas moderadas. Crece bien a temperaturas medias. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.61; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Zanahoria</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Daucus carota</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Apiaceae</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Invierno</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>16-18</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Raiz</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Cebolla;Lechuga;Tomate</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Hinojo</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Hortícola</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>Siembra directa únicamente; no trasplantar</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Siembra directa únicamente; no trasplantar. Misma familia que apio y perejil. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Cebolla</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Allium cepa</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Amaryllidaceae</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Invierno</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>13-24</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>Repelente</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>Zanahoria;Lechuga;Tomate</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>Poroto;Arveja</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>Hortícola intensivo</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Almácigo 60 días; repelente natural por sulfuros volátiles</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="n">
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>Almácigo 60 días; repelente natural por sulfuros volátiles. Mayor crecimiento con 20-25°C. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.75; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Ajo</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Allium sativum</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Amaryllidaceae</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Invierno</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="I13" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>13-24</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Repelente</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>Tomate;Frambuesa</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Poroto</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>Hortícola</t>
         </is>
       </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>Plantación de dientes; potente repelente y fungicida natural (alicina)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>Plantación de dientes; potente repelente y fungicida natural (alicina). Cultivo de invierno. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Pepino</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Cucumis sativus</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Cucurbitaceae</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Verano</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>21-27</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>Produccion</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>Poroto;Girasol;Rábano</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>Papa</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>Hortícola</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Asociar con poroto para fijar N; girasol como tutorado natural</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="3" t="n">
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>Asociar con poroto para fijar N; girasol como tutorado natural. Sensible a heladas. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Remolacha</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Beta vulgaris</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Amaranthaceae</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I15" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Raiz</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Lechuga;Cebolla</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>Espinaca</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Hortícola</t>
         </is>
       </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>Buena bordura de huerta; cosecha a los 70 días</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>Bordura de huerta. Semillas no germinan &lt;4°C; óptimo germinación 15-20°C. Cosecha 60-90 días. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.101; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Arveja</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Pisum sativum</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Invierno</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>Fijacion_N</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>Zanahoria;Rábano;Espinaca</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>Cebolla;Ajo</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>Hortícola</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Fija N; trepa en tutorado o maíz seco; cultivo de estación fría</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="3" t="n">
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>Fija N; trepa en tutorado o maíz seco. Cosecha oct-nov; decae con altas temperaturas. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, pp.83-85; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Brócoli</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Brassica oleracea var. italica</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Brassicaceae</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Invierno</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>15-20</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Produccion</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>Cebolla;Apio;Caléndula</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>Frutilla</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>Hortícola</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>Rotación obligatoria; no repetir Brassicas en mismo cantero</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>Rotación obligatoria; no repetir Brassicas. Tolera hasta 4-5°C; inflorescencias necesitan ~18°C. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.73; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Repollo</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Brassica oleracea var. capitata</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Brassicaceae</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Invierno</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>15-24</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>Produccion</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>Cebolla;Caléndula;Apio</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>Frutilla</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>Hortícola</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Muy beneficiado por caléndula anti-nemátodos en bordura</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="3" t="n">
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>Muy beneficiado por caléndula anti-nemátodos. Tolera hasta 4-5°C; óptimo vegetativo 22°C. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.73; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Apio</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Apium graveolens</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Apiaceae</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Secundario</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>15-21</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Produccion</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Tomate;Brócoli;Repollo</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>Hortícola</t>
         </is>
       </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>Ahuyenta mariposa de la col; combina bien con Brassicaceae</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>Ahuyenta mariposa de la col; combina bien con Brassicaceae. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Rábano</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Raphanus sativus</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Brassicaceae</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Secundario</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K20" s="2" t="n">
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Trampa</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Zanahoria;Pepino;Arveja</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Hinojo</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Todo Uruguay</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Hortícola</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>Cultivo trampa para pulgones; ciclo muy corto (~20 días). Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Zapallito</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Cucurbita pepo</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Cucurbitaceae</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Verano</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>18-24</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Cobertura</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Maíz;Poroto</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Hortícola</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>Variante compacta del zapallo; cobertura de suelo. Sensible a heladas. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Coliflor</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Brassica oleracea var. botrytis</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Brassicaceae</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Invierno</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>15-21</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Produccion</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Cebolla;Apio;Caléndula</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Frutilla</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Hortícola</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>Rotación obligatoria con otras Brassicaceae. Tolera 4-5°C; inflorescencias ~18°C. Cosecha 90-100 días post-trasplante. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.73; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Puerro</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Allium porrum</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Amaryllidaceae</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Invierno</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>20-24</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Produccion</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Zanahoria;Apio</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>Hortícola</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>Almácigo junio-julio; trasplante a los 3 meses; cosecha desde 90 días. Misma familia que cebolla y ajo. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, tabla resumen; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Haba</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Vicia faba</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Fabaceae</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Invierno</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>15-25</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Fijacion_N</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Maíz;Zanahoria</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Hortícola</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>Cultivo de invierno; fija N atmosférico. Siembra abril-julio. Cosecha oct-nov (decae con calor). Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, pp.83-85; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Frutilla</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Fragaria x ananassa</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Rosaceae</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Otoño</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>15-26</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Produccion</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Ajo;Espinaca;Borraja</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Brócoli;Repollo</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>Hortícola</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>Trasplante fin de marzo-abril sobre camellones. Cosecha primavera (5-6 meses). Se multiplica por estolones. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, pp.53-54; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Kale</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Brassica oleracea var. acephala</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Brassicaceae</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>15-20</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Produccion</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Cebolla;Caléndula;Apio</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Hortícola</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>Muy resistente a heladas. Almácigos y trasplante. Cosecha 90 días; hojas basales escalonadas. Siembra feb-mayo (CE). Ref: Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay; FAGRO-IMM (2002). Huertas Comunitarias. Citado en CE (2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Boniato</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Ipomoea batatas</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Convolvulaceae</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Verano</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Raiz</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Maíz</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>Hortícola</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>Trasplante post 1 oct para escapar heladas. Curado post-cosecha: 28-30°C, 90% humedad, 6-8 días. Conservación: 13-15°C. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, pp.69-71; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Sandía</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Citrullus lanatus</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Cucurbitaceae</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Verano</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>21-29</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Produccion</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Maíz</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Hortícola</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>Muy sensible a heladas; requiere ~4 meses libres de heladas. Cosecha 80-120 días. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, pp.105-106; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>Trampa</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Zanahoria;Pepino;Arveja</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Hinojo</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Melón</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Cucumis melo</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Cucurbitaceae</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Verano</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>21-32</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Produccion</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Maíz;Zapallo</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>Hortícola</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>Muy sensible al frío; la helada la quema. Semillas germinan rápido a 20-25°C. Cosecha 3,5-4 meses. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.88; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Maíz dulce</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Zea mays var. saccharata</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Poaceae</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Verano</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>&gt;15</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Produccion</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Poroto;Zapallo;Calabaza</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Hortícola;Policultivo</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>Sensible a heladas; siembra set-feb escalonada quincenal. Compañero del poroto y zapallo. Cosecha 90-100 días. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, pp.87-88; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Albahaca</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Ocimum basilicum</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Lamiaceae</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Verano</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Secundario</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>18-30</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Repelente</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Tomate;Morrón;Pepino</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>Hortícola</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Cultivo trampa para pulgones; ciclo muy corto (30 días)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Zapallito</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Cucurbita pepo</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Cucurbitaceae</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Verano</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>Repelente de mosca blanca y pulgones por aceites esenciales. Intercalar con tomate. Sensible a heladas. Cosecha 30-40 días. Ref: Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay; FAGRO-IMM (2002). Huertas Comunitarias. Citado en CE (2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Perejil</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Petroselinum crispum</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Apiaceae</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Secundario</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Produccion</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Tomate;Espárrago</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Cebolla;Ajo</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Todo Uruguay</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Hortícola</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>Siembra directa todo el año en camellones. Primer corte a los 60 días. Bienal. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, tabla resumen; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Rúcula</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Eruca vesicaria</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Brassicaceae</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Secundario</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I21" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>Cobertura</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>Maíz;Poroto</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>Sur;Litoral</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>25-27</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Produccion</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Zanahoria;Pepino;Lechuga</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Todo Uruguay</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>Hortícola</t>
         </is>
       </c>
-      <c r="Q21" s="3" t="inlineStr">
-        <is>
-          <t>Variante compacta del zapallo; cobertura de suelo</t>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>Ciclo corto (~40 días). Tiende a florecer con calor excesivo (bolting). Siembra directa o almácigo. Ref: Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay; FAGRO-IMM (2002). Huertas Comunitarias. Citado en CE (2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Nabo</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Brassica rapa var. rapa</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Brassicaceae</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Secundario</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>15-20</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Raiz</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Arveja;Poroto</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Todo Uruguay</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Hortícola</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>Siembra directa todo el año; cosecha 30-45 días. Tolera frío moderado. Ref: Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, tabla resumen; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
         </is>
       </c>
     </row>
@@ -2164,7 +3006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2180,762 +3022,972 @@
     <col width="26" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="38" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Nombre_cientifico</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Familia</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Funcion_principal</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Funcion_secundaria</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Atrae_polinizadores</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Polinizadores_especificos</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Control_plagas</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Mecanismo</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Estacion</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Region_Uruguay</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Caléndula</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Calendula officinalis</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Flor</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Nematicida</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Atraccion polinizadores</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Abejas;Mariposas</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Nematodos;Trips</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Exudados radiculares (tiofenos)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Bordura clásica entre tomates y repollos. Ref: Marotti et al. (2010), J. of the Science of Food and Agriculture, Vol.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Bordura clásica entre tomates y repollos. Ref: Marotti et al. (2010). J. Sci. Food Agric. Vol.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Tagete</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Tagetes spp.</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Flor</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Repelente</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Nematicida</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Abejas;Sírfidos</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Mosca blanca;Nematodos;Pulgones</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Compuestos volátiles (alfa-terthienyl)</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Verano</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>No confundir con Caléndula; repelente aéreo. Ref: Marotti et al. (2010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>No confundir con Caléndula; repelente aéreo. Ref: Marotti et al. (2010). J. Sci. Food Agric. Vol.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Albahaca</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Ocimum basilicum</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Lamiaceae</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Aromática</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Repelente</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Mejora desarrollo tomate</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Abejas</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Mosca blanca;Áfidos</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Aceites esenciales volátiles</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Verano</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Plantar intercalada con tomate; retirar flores para mantener aceites activos</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="n">
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Plantar intercalada con tomate; retirar flores para mantener aceites activos. Ver también Cultivos_Horticolas ID30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Lavanda</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Lavandula angustifolia</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Lamiaceae</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Aromática</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Atraccion polinizadores</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Repelente de polillas</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Abejas;Mariposas;Abejorros</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Polillas</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Aroma repelente</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Perenne; excelente en bordes permanentes de huerta y sistemas agroforestales</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Romero</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Salvia rosmarinus</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Lamiaceae</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Aromática</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Repelente</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Atraccion polinizadores</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Abejas</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Plagas de Brassicaceae</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>Aceites esenciales</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Perenne; protege repollos y brócoli; bueno en bordes de huerta</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="n">
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Borraja</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Borago officinalis</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Boraginaceae</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Flor</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Atraccion polinizadores</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Acumulador mineral</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Abejorros;Abejas</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Acumula silicio y calcio en suelo</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Verano</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Autorresiembra; flores comestibles; beneficia frutillas</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Nasturtium</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Tropaeolum majus</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Tropaeolaceae</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Flor</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Trampa</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Cobertura suelo</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Abejas;Mariposas</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Pulgones;Mosca blanca</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>Planta trampa que concentra plagas</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Dejar como trampa y retirar con plaga; flores y hojas comestibles</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="n">
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Dejar como trampa y retirar con plaga; flores y hojas comestibles. Ref: ATTRA-NCAT. Companion Planting. National Sustainable Agriculture Information Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Girasol</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Helianthus annuus</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Flor</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Soporte fisico;Atraccion polinizadores</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Banco de insectos beneficos</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Abejas;Mariposas</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Hospeda insectos benéficos en disco floral</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Verano</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Tutorado natural para pepino y poroto; hasta 200cm de altura</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Hinojo</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Foeniculum vulgare</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Apiaceae</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Aromática</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Atraccion enemigos naturales</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>Sírfidos;Avispas parasitoides</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>Pulgones (indirecto)</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>Atrae depredadores de plagas</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>ALELOPÁTICO con la mayoría de hortalizas — plantar solo en bordes alejados</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="3" t="n">
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Ortiga</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Urtica dioica</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Urticaceae</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Herbacea</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Activador compost</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Acumulador mineral</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Pulgones (trampa)</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Concentra pulgones lejos del cultivo</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>Hacer purín como fertilizante foliar; no plantar dentro de cultivos</t>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>Hacer purín como fertilizante foliar (macerado 1kg/10L agua, 48hs). No plantar dentro de cultivos. Ref: Zoppolo et al. (2008), p.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Tomillo</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Thymus vulgaris</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Lamiaceae</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Aromática</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Repelente</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Atraccion polinizadores</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Abejas;Mariposas</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Plagas de Brassicaceae;Mosca blanca</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Aceites esenciales (timol)</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Perenne; protege cultivos de Brassicaceae. Combina bien con brócoli, repollo, coliflor. Ref: Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay; FAGRO-IMM (2002). Huertas Comunitarias. Citado en CE (2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Orégano</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Origanum vulgare</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Lamiaceae</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Aromática</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Repelente</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Atraccion polinizadores</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Abejas;Mariposas</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Pulgones;Áfidos</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Aceites esenciales volátiles</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>Perenne; repelente general. Plantado en borduras mejora el sabor de cultivos vecinos. Ref: Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay; FAGRO-IMM (2002). Huertas Comunitarias. Citado en CE (2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Ciboulette</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Allium schoenoprasum</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Amaryllidaceae</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Aromática</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Repelente</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Atraccion polinizadores</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Abejas</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Pulgones;Áfidos</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Compuestos azufrados</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Misma familia que cebolla y ajo; actúa como repelente. Bordura ideal con frutillas y zanahorias. Ref: Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay; FAGRO-IMM (2002). Huertas Comunitarias. Citado en CE (2023)</t>
         </is>
       </c>
     </row>
@@ -2950,7 +4002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2967,773 +4019,980 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="38" customWidth="1" min="15" max="15"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Nombre_cientifico</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Familia</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Nativo</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Funcion_principal</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Funciones_secundarias</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Sombra_1_3</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Fauna_asociada</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Velocidad_crecimiento</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Altura_adulto_m</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Distancia_min_cultivo_m</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>Region_Uruguay</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Sistema_productivo</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Coronilla</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Scutia buxifolia</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Rhamnaceae</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Biodiversidad</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Cortina forestal;Refugio fauna</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Aves;Reptiles</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Lenta</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Cortinas;Agroforestal;Silvopastoril</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Madera muy dura; nativo; excelente cortina viva</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="n">
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Tala</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Celtis tala</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Cannabaceae</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Biodiversidad</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Fruto para fauna;Sombra moderada</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Aves;Mamiferos pequeños</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Litoral;Sur;Este</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Silvopastoril;Agroforestal;Bordes</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Fruto consumido por aves; nativo del litoral y sur</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Espinillo</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Vachellia caven</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Fijacion_N</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Sombra;Melifera</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Abejas;Mariposas</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Silvopastoril;Agroforestal;Huerta</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Florece en invierno; muy melífera; fija N2; nativo</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="n">
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Pitanga</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Eugenia uniflora</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Myrtaceae</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Frutal nativo</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Biodiversidad;Medicinal</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Aves;Mariposas</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Lenta</t>
         </is>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Sur;Litoral</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Huerta agroforestal;Bordura</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>Frutal nativo comestible; gran atractivo de aves; medicinal</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Guayabo del pais</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Acca sellowiana</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Myrtaceae</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Frutal nativo</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Atraccion polinizadores;Medicinal</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Abejas;Colibries</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Lenta</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>Sur;Este</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Huerta agroforestal</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>Fruto muy nutritivo; flores melíferas; atrae colibríes; nativo</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="n">
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Sauce criollo</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Salix humboldtiana</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Salicaceae</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Cortina hidraulica</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Control erosion;Fauna riparia</t>
         </is>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Aves acuaticas</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Rapida</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Litoral;Sur;Este</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Bordes de agua;Cortinas</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Solo en bordes de cursos de agua; nativo</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Timbo</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Enterolobium contortisiliquum</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Sombra</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Fijacion_N;Madera</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Aves;Mamiferos</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Rapida</t>
         </is>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>Norte;Litoral Norte</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>Silvopastoril</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>Árbol imponente; sombra muy densa; solo norte del país; nativo</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="n">
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Ceibo</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Erythrina crista-galli</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Biodiversidad</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Melifera;Flor nacional</t>
         </is>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Picaflores;Abejas</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Bordura;Agroforestal ornamental</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>Flor nacional; atrae colibríes; crece en suelos húmedos; nativo</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Algarrobo</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Prosopis affinis</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Fijacion_N;Sombra</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Frutal nativo;Forrajero</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>Aves;Mamiferos</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="K10" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="L10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>Norte;Litoral Norte</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>Silvopastoril;Agroforestal</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>Vainas nutritivas consumidas por ganado; fija N; nativo del norte</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="3" t="n">
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Cedrón del monte</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Aloysia gratissima</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Verbenaceae</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Melifera</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Medicinal;Aromatica</t>
         </is>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Abejas;Mariposas</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>Sur;Litoral;Este</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Huerta agroforestal;Medicinal</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>Nativo; medicinal; muy melífera; apto para sotobosque de huerta</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Arazá</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Psidium cattleianum</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Myrtaceae</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Frutal nativo</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Biodiversidad;Melifera</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Aves;Mariposas</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Sur;Litoral;Este</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Huerta agroforestal;Bordura</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>Frutal nativo comestible; fruto rico en vitamina C; atrae aves. Resiste heladas moderadas. Ref: Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Mburucuyá</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Passiflora caerulea</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Passifloraceae</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Atraccion polinizadores</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Frutal nativo;Cobertura</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Abejas;Mariposas;Picaflores</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Sur;Litoral;Este</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>Huerta agroforestal;Bordura</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>Frutal nativo trepador; flores muy melíferas. Hábitat de mariposas. Ref: Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Sarandí blanco</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Phyllanthus sellowianus</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Phyllanthaceae</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Cortina hidraulica</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Biodiversidad;Control erosion</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Aves acuaticas;Anfibios</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Litoral;Sur;Este</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Bordes de agua;Cortinas</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>Nativo ripario; control de erosión de márgenes. Hábitat de fauna acuática</t>
         </is>
       </c>
     </row>
@@ -3748,7 +5007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3763,514 +5022,640 @@
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Arbol</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Nombre_cientifico</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Animal</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Tipo_produccion</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Sombra_verano</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Resistencia_sequia</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Arboles_por_ha</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Beneficio_productivo</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Funcion_ecologica</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Region_Uruguay</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>Epoca_implantacion</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Espinillo</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Vachellia caven</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Bovino</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Carne;Leche</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Sombra verano; produccion miel</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Fijacion N; refugio polinizadores</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Otono-invierno</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Reduce estrés calórico; mejora conversión alimenticia</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="n">
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Coronilla</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Scutia buxifolia</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Ovino</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Lana;Carne</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Refugio ante heladas y viento</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Biodiversidad;Cortaviento</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Sur;Litoral;Este</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Otono</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Cortina rompe vientos; reduce consumo de forraje</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Tala</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Celtis tala</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Bovino</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Carne</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Sombra moderada</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Refugio fauna;Biodiversidad</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Litoral;Sur</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Primavera</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Sistema extensivo; distancias amplias entre árboles</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="n">
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Algarrobo</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Prosopis affinis</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Bovino</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Carne</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Muy alta</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Vaina forrajera consumida por ganado</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Fijacion N; sombra</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Norte;Litoral Norte</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Primavera</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Vainas nutritivas consumidas directamente; muy resistente a sequía</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Timbo</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Enterolobium contortisiliquum</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Bovino</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Carne</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Muy alta</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Sombra intensa verano</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Fijacion N; biodiversidad</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>Norte</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>Primavera</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>Solo norte del país; distancias amplias por tamaño adulto (20m)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="n">
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Sauce criollo</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Salix humboldtiana</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Bovino</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Leche</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Sombra en bordes de aguadas</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Control erosion hidrica</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Litoral;Sur;Este</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Otono-invierno</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Solo en áreas con agua disponible; raíces invasivas</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Ceibo</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Erythrina crista-galli</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Bovino;Ovino</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Carne;Lana</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Sombra moderada; atraccion fauna</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Biodiversidad;Melifera</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>Todo Uruguay</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>Primavera</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>Flor nacional; crece bien en suelos húmedos; ornamental</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Guayabo del pais</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Acca sellowiana</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Bovino;Ovino</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Carne;Miel</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Sombra moderada; fruto apetecido por fauna</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Atraccion polinizadores;Biodiversidad</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Sur;Este</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Otono</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Frutal nativo; sistema silvopastoril diversificado; muy melífero</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Pitanga</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Eugenia uniflora</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Bovino</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Carne</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Sombra en borduras; fruto para fauna</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Biodiversidad;Melifera</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Sur;Litoral</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Frutal nativo; uso en borduras de potreros; atrae aves beneficiosas</t>
         </is>
       </c>
     </row>
@@ -4285,7 +5670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4297,758 +5682,1158 @@
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Especie_A</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Especie_B</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Relacion</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Intensidad</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Mecanismo</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Beneficio_A</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Beneficio_B</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Sistema</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Tomate</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Albahaca</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Positiva</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Fuerte</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Volatiles repelentes (aceites esenciales)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Menos mosca blanca</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Mejor crecimiento</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Horticola</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>ATTRA-NCAT; literatura agroecologica</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>ATTRA-NCAT. Companion Planting. National Sustainable Agriculture Information Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Tomate</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Calendula</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Positiva</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Fuerte</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Exudados radiculares (tiofenos nematicidas)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Menos nematodos</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Floración atrapa plagas</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Horticola</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Marotti et al. (2010), J. Science Food Agric. Vol.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Marotti et al. (2010). J. Sci. Food Agric. Vol.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Maiz</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Poroto</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Positiva</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Fuerte</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Fijacion N2; soporte fisico</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Soporte para trepar</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>N disponible en suelo</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Horticola;Policultivo</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Conocimiento indigena mesoamericano (3 Hermanas)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="n">
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Maiz</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Zapallo</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Positiva</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Cobertura de suelo; conservacion humedad</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Menos evapotranspiracion</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Cobertura protectora</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Horticola;Policultivo</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Conocimiento indigena mesoamericano (3 Hermanas)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Tomate</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Papa</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Negativa</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Fuerte</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Enfermedades compartidas (Phytophthora infestans)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Riesgo tizon tardio</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Riesgo tizon tardio</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Horticola</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Fitopatologia clasica; INIA Uruguay</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="n">
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Hinojo</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Tomate</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Negativa</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Fuerte</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Aleloquimicos (anetol)</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Inhibicion crecimiento</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Inhibicion crecimiento</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Horticola</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Alelopatia vegetal documentada</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Zanahoria</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Cebolla</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Positiva</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Fuerte</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Repelencia cruzada (sulfuros vs terpenos)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Repele mosca cebolla</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Repele mosca zanahoria</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Horticola</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Permacultura clasica; Louise Riotte, Companion Planting (1975)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="n">
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Riotte, L. (1975). Companion Planting. Garden Way Publishing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Poroto</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Cebolla</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Negativa</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Competencia quimica (sulfuros inhiben nodulacion)</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Inhibicion fijacion N</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Menor rendimiento poroto</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Horticola</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Literatura agronomica</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Espinillo</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Cultivos horticolas</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Positiva</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Microclima; sombra parcial; fijacion N2</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Menos estres termico</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Mejora estructura suelo</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>Agroforestal;Horticola</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>Sistemas agroforestales Cono Sur</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="3" t="n">
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Calendula</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Brassicaceae (repollo;brocoli)</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Positiva</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Fuerte</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Nematicida + repelente Lepidopteros</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Menos Pieris brassicae</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Proteccion quimica raices</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Horticola</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Marotti et al. (2010); agricultura organica</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Marotti et al. (2010). J. Sci. Food Agric. Vol.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Ajo</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Tomate</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Positiva</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Fungicida natural (alicina)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Menos hongos foliares</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Mejor sabor</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Horticola</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>Biofungicidas naturales documentados</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="n">
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Arveja</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Zanahoria</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Positiva</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Fijacion N + uso diferencial del suelo</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>N disponible</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Soporte suave</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Horticola</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Horticultura ecologica</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Timbo</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Pasturas</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Positiva</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Fuerte</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Sombra; fijacion N2; microclima</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Menos estres calórico animal</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Mejora fertilidad suelo</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>Silvopastoril</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>Sistemas silvopastoriles del norte de Uruguay</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="3" t="n">
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Nasturtium</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Cultivos hortícolas</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Positiva</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Planta trampa (concentra pulgones y mosca blanca)</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Proteccion cultivo principal</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Cobertura de suelo</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Horticola</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>ATTRA-NCAT; permacultura</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>ATTRA-NCAT. Companion Planting. National Sustainable Agriculture Information Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Haba</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Maíz dulce</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Positiva</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Fuerte</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Fijacion N2; uso diferencial del suelo</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>N disponible post-cultivo</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Mejor estructura suelo</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Horticola</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.88: la planta de maíz produce más si el cultivo anterior fue de arvejas o habas</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Frutilla</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Ajo</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Positiva</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Fuerte</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Fungicida natural (alicina); repelente de plagas</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Menos hongos y plagas</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Asociación beneficiosa documentada</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Horticola</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.64; Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Kale</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Caléndula</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Positiva</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Fuerte</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Nematicida + repelente Lepidopteros en bordura</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Menos Pieris brassicae</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Floración atrae polinizadores</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Horticola</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Marotti et al. (2010). J. Sci. Food Agric. Vol.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Boniato</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Maíz</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Positiva</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Cobertura de suelo; sombra parcial</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Protección contra malezas</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Aprovechamiento espacial</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Horticola;Policultivo</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Espinillo</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Bovinos</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Positiva</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Fuerte</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Sombra; regulacion termica; fijacion N</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Menor estrés calórico</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Mejora fertilidad pastura</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Silvopastoril</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Sistemas silvopastoriles Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Brócoli</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Negativa</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Misma área = acumulación patógenos; rotación necesaria</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Riesgo enfermedades fúngicas</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Riesgo enfermedades fúngicas</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Horticola</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Zoppolo et al. (2008). Alimentos en la Huerta. INIA-OPS-UDELAR. ISBN 978-9974-38-262-6, p.73: rotación obligatoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Albahaca</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Morrón</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Positiva</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Aceites esenciales volátiles repelentes</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Menos mosca blanca</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Mejor crecimiento reportado</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Horticola</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Centro Emmanuel (2023). Calendario de Siembra. Red de Agroecología Uruguay; FAGRO-IMM (2002). Huertas Comunitarias. Citado en CE (2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Romero</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Brassicaceae</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Positiva</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Aceites esenciales (borneol, alcanfor) repelentes</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Menos plagas foliares</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Atraccion polinizadores</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Horticola</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Horticultura ecologica; aromáticas como repelentes</t>
         </is>
       </c>
     </row>
